--- a/output/pdf_financials_xlsx/FNR.xlsx
+++ b/output/pdf_financials_xlsx/FNR.xlsx
@@ -2373,28 +2373,28 @@
         <v>1.01</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="35">
@@ -2483,28 +2483,28 @@
         <v>1.01</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="37">
@@ -3143,28 +3143,28 @@
         <v>9.856</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>12.697</v>
+        <v>12.612</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>13.226</v>
+        <v>13.191</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>8.045</v>
+        <v>7.982</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>7.669</v>
+        <v>7.618</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.5</v>
+        <v>9.455</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>7.193</v>
+        <v>7.129</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>7.284</v>
+        <v>7.228</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7.815</v>
+        <v>7.735</v>
       </c>
     </row>
     <row r="49">
@@ -7398,16 +7398,16 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.079</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.076</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7455,16 +7455,16 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.079</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.076</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29882,7 +29882,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FNR.xlsx
+++ b/output/pdf_financials_xlsx/FNR.xlsx
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -6699,13 +6699,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -33170,7 +33170,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -39680,7 +39684,11 @@
           <t>Proceeds from disposal of property plant &amp; equipment</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
